--- a/术语表&画面字.xlsx
+++ b/术语表&画面字.xlsx
@@ -1287,7 +1287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP322"/>
+  <dimension ref="A1:AP400"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.25" defaultRowHeight="14"/>
   <cols>
     <col width="13.4166666666667" customWidth="1" style="3" min="1" max="1"/>
@@ -4630,9 +4630,21 @@
           <t>EP38 00:00:13,638 --&gt; 00:00:15,515</t>
         </is>
       </c>
-      <c r="H41" s="23" t="n"/>
-      <c r="I41" s="23" t="n"/>
-      <c r="J41" s="23" t="n"/>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>ten million dollars</t>
+        </is>
+      </c>
+      <c r="I41" s="23" t="inlineStr">
+        <is>
+          <t>diez millones de dólares</t>
+        </is>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>EP47 00:00:03,962 --&gt; 00:00:05,130</t>
+        </is>
+      </c>
       <c r="K41" s="30" t="n"/>
       <c r="L41" s="19" t="n"/>
       <c r="M41" s="19" t="n"/>
@@ -4695,9 +4707,21 @@
           <t>EP39 00:00:21,438 --&gt; 00:00:22,981</t>
         </is>
       </c>
-      <c r="H42" s="23" t="n"/>
-      <c r="I42" s="23" t="n"/>
-      <c r="J42" s="23" t="n"/>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>Super Bowl</t>
+        </is>
+      </c>
+      <c r="I42" s="23" t="inlineStr">
+        <is>
+          <t>Super Bowl</t>
+        </is>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>EP48 00:00:44,669 --&gt; 00:00:46,129</t>
+        </is>
+      </c>
       <c r="K42" s="19" t="n"/>
       <c r="L42" s="19" t="n"/>
       <c r="M42" s="19" t="n"/>
@@ -4764,9 +4788,21 @@
           <t>EP4 00:00:23,523 --&gt; 00:00:24,733</t>
         </is>
       </c>
-      <c r="H43" s="31" t="n"/>
-      <c r="I43" s="31" t="n"/>
-      <c r="J43" s="31" t="n"/>
+      <c r="H43" s="31" t="inlineStr">
+        <is>
+          <t>NFL</t>
+        </is>
+      </c>
+      <c r="I43" s="31" t="inlineStr">
+        <is>
+          <t>NFL</t>
+        </is>
+      </c>
+      <c r="J43" s="31" t="inlineStr">
+        <is>
+          <t>EP48 00:00:29,946 --&gt; 00:00:31,489</t>
+        </is>
+      </c>
       <c r="K43" s="32" t="n"/>
       <c r="L43" s="33" t="n"/>
       <c r="M43" s="33" t="n"/>
@@ -4833,9 +4869,21 @@
           <t>EP40 00:00:12,053 --&gt; 00:00:14,556</t>
         </is>
       </c>
-      <c r="H44" s="31" t="n"/>
-      <c r="I44" s="31" t="n"/>
-      <c r="J44" s="31" t="n"/>
+      <c r="H44" s="31" t="inlineStr">
+        <is>
+          <t>Touchdown</t>
+        </is>
+      </c>
+      <c r="I44" s="31" t="inlineStr">
+        <is>
+          <t>Touchdown</t>
+        </is>
+      </c>
+      <c r="J44" s="31" t="inlineStr">
+        <is>
+          <t>EP5 00:00:30,739 --&gt; 00:00:31,698</t>
+        </is>
+      </c>
       <c r="K44" s="33" t="n"/>
       <c r="L44" s="33" t="n"/>
       <c r="M44" s="33" t="n"/>
@@ -4902,9 +4950,21 @@
           <t>EP41 00:00:36,286 --&gt; 00:00:37,954</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Final Four</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Semifinales</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>EP6 00:00:04,713 --&gt; 00:00:05,547</t>
+        </is>
+      </c>
       <c r="K45" s="33" t="n"/>
       <c r="L45" s="33" t="n"/>
       <c r="M45" s="33" t="n"/>
@@ -4967,9 +5027,21 @@
           <t>EP42 00:00:02,877 --&gt; 00:00:04,838</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>five hundred</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>quinientos</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>EP8 00:01:26,669 --&gt; 00:01:28,129</t>
+        </is>
+      </c>
       <c r="K46" s="33" t="n"/>
       <c r="L46" s="33" t="n"/>
       <c r="M46" s="33" t="n"/>
@@ -5032,9 +5104,21 @@
           <t>EP43 00:00:00,417 --&gt; 00:00:02,252</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>million</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>millón</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>EP9 00:00:06,923 --&gt; 00:00:08,883</t>
+        </is>
+      </c>
       <c r="K47" s="33" t="n"/>
       <c r="L47" s="33" t="n"/>
       <c r="M47" s="33" t="n"/>
@@ -5097,9 +5181,21 @@
           <t>EP43 00:00:59,768 --&gt; 00:01:01,770</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>three million</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>tres millones</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>EP9 00:00:06,923 --&gt; 00:00:08,883</t>
+        </is>
+      </c>
       <c r="K48" s="33" t="n"/>
       <c r="L48" s="33" t="n"/>
       <c r="M48" s="33" t="n"/>
@@ -5162,9 +5258,21 @@
           <t>EP44 00:00:00,375 --&gt; 00:00:01,418</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>thirty million dollars</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>treinta millones de dólares</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>EP9 00:02:37,407 --&gt; 00:02:38,658</t>
+        </is>
+      </c>
       <c r="K49" s="33" t="n"/>
       <c r="L49" s="33" t="n"/>
       <c r="M49" s="33" t="n"/>
@@ -5231,9 +5339,21 @@
           <t>EP44 00:00:18,643 --&gt; 00:00:19,561</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>forty million</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>cuarenta millones</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>EP9 00:02:40,577 --&gt; 00:02:41,286</t>
+        </is>
+      </c>
       <c r="K50" s="33" t="n"/>
       <c r="L50" s="33" t="n"/>
       <c r="M50" s="33" t="n"/>
@@ -5480,9 +5600,21 @@
           <t>EP35 00:00:30,238 --&gt; 00:00:31,656</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="34" t="n"/>
-      <c r="G54" s="2" t="n"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>NFL</t>
+        </is>
+      </c>
+      <c r="F54" s="34" t="inlineStr">
+        <is>
+          <t>NFL</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>EP47 00:00:07,132 --&gt; 00:00:08,925</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
       <c r="J54" s="2" t="n"/>
@@ -5533,9 +5665,21 @@
           <t>EP35 00:00:49,049 --&gt; 00:00:50,633</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="34" t="n"/>
-      <c r="G55" s="2" t="n"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>NFL</t>
+        </is>
+      </c>
+      <c r="F55" s="34" t="inlineStr">
+        <is>
+          <t>NFL</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>EP48 00:00:29,946 --&gt; 00:00:31,489</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
       <c r="J55" s="2" t="n"/>
@@ -5586,9 +5730,21 @@
           <t>EP35 00:00:49,049 --&gt; 00:00:50,633</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="34" t="n"/>
-      <c r="G56" s="2" t="n"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Super Bowl</t>
+        </is>
+      </c>
+      <c r="F56" s="34" t="inlineStr">
+        <is>
+          <t>Super Bowl</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>EP48 00:00:44,669 --&gt; 00:00:46,129</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="n"/>
       <c r="J56" s="2" t="n"/>
@@ -5639,9 +5795,21 @@
           <t>EP35 00:00:56,806 --&gt; 00:00:58,433</t>
         </is>
       </c>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="34" t="n"/>
-      <c r="G57" s="2" t="n"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Knights</t>
+        </is>
+      </c>
+      <c r="F57" s="34" t="inlineStr">
+        <is>
+          <t>Caballeros</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>EP5 00:00:48,548 --&gt; 00:00:50,091</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
       <c r="J57" s="2" t="n"/>
@@ -5692,9 +5860,21 @@
           <t>EP35 00:01:22,999 --&gt; 00:01:23,750</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="34" t="n"/>
-      <c r="G58" s="2" t="n"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>The Knights</t>
+        </is>
+      </c>
+      <c r="F58" s="34" t="inlineStr">
+        <is>
+          <t>Los Caballeros</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>EP6 00:00:00,208 --&gt; 00:00:02,377</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
       <c r="J58" s="2" t="n"/>
@@ -5749,7 +5929,21 @@
           <t>EP36 00:00:10,593 --&gt; 00:00:11,594</t>
         </is>
       </c>
-      <c r="F59" s="35" t="n"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>The Eagles</t>
+        </is>
+      </c>
+      <c r="F59" s="35" t="inlineStr">
+        <is>
+          <t>Los Águilas</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>EP6 00:00:07,799 --&gt; 00:00:10,427</t>
+        </is>
+      </c>
       <c r="K59" s="33" t="n"/>
       <c r="L59" s="33" t="n"/>
       <c r="M59" s="33" t="n"/>
@@ -5801,7 +5995,21 @@
           <t>EP37 00:00:54,763 --&gt; 00:00:57,140</t>
         </is>
       </c>
-      <c r="F60" s="35" t="n"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Knights</t>
+        </is>
+      </c>
+      <c r="F60" s="35" t="inlineStr">
+        <is>
+          <t>Caballeros</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>EP7 00:00:00,875 --&gt; 00:00:02,210</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>a worthless cripple.</t>
@@ -5849,7 +6057,21 @@
           <t>EP37 00:00:48,506 --&gt; 00:00:50,133</t>
         </is>
       </c>
-      <c r="F61" s="35" t="n"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Eagles</t>
+        </is>
+      </c>
+      <c r="F61" s="35" t="inlineStr">
+        <is>
+          <t>Águilas</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>EP7 00:01:12,572 --&gt; 00:01:14,199</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>Hang on.</t>
@@ -5897,7 +6119,21 @@
           <t>EP37 00:00:53,511 --&gt; 00:00:54,596</t>
         </is>
       </c>
-      <c r="F62" s="35" t="n"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Eagles</t>
+        </is>
+      </c>
+      <c r="F62" s="35" t="inlineStr">
+        <is>
+          <t>Águilas</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>EP8 00:00:03,712 --&gt; 00:00:04,838</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
           <t>It was a fluke.</t>
@@ -5945,7 +6181,21 @@
           <t>EP37 00:00:57,307 --&gt; 00:00:59,142</t>
         </is>
       </c>
-      <c r="F63" s="35" t="n"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Knights</t>
+        </is>
+      </c>
+      <c r="F63" s="35" t="inlineStr">
+        <is>
+          <t>Caballeros</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>EP8 00:00:47,255 --&gt; 00:00:47,964</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>Look at the score.</t>
@@ -5993,7 +6243,21 @@
           <t>EP38 00:00:00,333 --&gt; 00:00:02,711</t>
         </is>
       </c>
-      <c r="F64" s="35" t="n"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Eagles</t>
+        </is>
+      </c>
+      <c r="F64" s="35" t="inlineStr">
+        <is>
+          <t>Águilas</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>EP9 00:00:19,269 --&gt; 00:00:21,646</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>Maybe he's just getting lucky.</t>
@@ -6041,7 +6305,21 @@
           <t>EP38 00:00:02,919 --&gt; 00:00:05,296</t>
         </is>
       </c>
-      <c r="F65" s="35" t="n"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Knights</t>
+        </is>
+      </c>
+      <c r="F65" s="35" t="inlineStr">
+        <is>
+          <t>Caballeros</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>EP9 00:01:01,603 --&gt; 00:01:03,438</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>I'm not gonna be slapped</t>
@@ -6853,6 +7131,21 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EP47 00:00:14,889 --&gt; 00:00:15,348</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>I have money.</t>
@@ -6880,6 +7173,26 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>main character</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EP48 00:00:07,674 --&gt; 00:00:08,299</t>
+        </is>
+      </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>But this game?</t>
@@ -6907,6 +7220,26 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ted Vincent</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ted Vincent</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Entrenador</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EP6 00:00:05,672 --&gt; 00:00:07,382</t>
+        </is>
+      </c>
       <c r="O85" t="inlineStr">
         <is>
           <t>Oh my goodness.</t>
@@ -6934,6 +7267,26 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>main character, informal: Ted</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>EP7 00:00:08,466 --&gt; 00:00:09,843</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>this is unreal.</t>
@@ -6961,6 +7314,26 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>character name, informal: James</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>EP7 00:00:14,097 --&gt; 00:00:15,640</t>
+        </is>
+      </c>
       <c r="O87" t="inlineStr">
         <is>
           <t>Because of you,</t>
@@ -6988,6 +7361,26 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Mr. Vincent</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Señor Vincent</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>honorific, surname: Vincent</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EP7 00:01:11,738 --&gt; 00:01:12,572</t>
+        </is>
+      </c>
       <c r="O88" t="inlineStr">
         <is>
           <t>After this game,</t>
@@ -7015,6 +7408,26 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>EP8 00:00:01,710 --&gt; 00:00:03,211</t>
+        </is>
+      </c>
       <c r="O89" t="inlineStr">
         <is>
           <t>you understand?</t>
@@ -7042,6 +7455,26 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>EP8 00:00:20,353 --&gt; 00:00:22,564</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr">
         <is>
           <t>Stop him!</t>
@@ -7069,6 +7502,26 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Mr. Vincent</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Señor Vincent</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Señor Vincent</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EP8 00:01:48,983 --&gt; 00:01:50,026</t>
+        </is>
+      </c>
       <c r="O91" t="inlineStr">
         <is>
           <t>to catch it.</t>
@@ -7096,6 +7549,26 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>EP9 00:00:28,570 --&gt; 00:00:29,821</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>Ted can't win.</t>
@@ -13329,6 +13802,2112 @@
       <c r="S322" t="inlineStr">
         <is>
           <t>00:01:54,072 --&gt; 00:01:54,906</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>Ten million dollars?</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>¿Diez millones de dólares?</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>Duración corta (959ms ≤ 1000ms) pero 26 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>00:00:09,426 --&gt; 00:00:10,385</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>I could work my whole life and</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>Podría trabajar toda mi vida y</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>Duración corta (917ms ≤ 1000ms) pero 30 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>00:00:12,012 --&gt; 00:00:12,929</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>never make that money.</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>nunca ganar esa cantidad.</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>Duración corta (793ms ≤ 1000ms) pero 25 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>00:00:12,929 --&gt; 00:00:13,722</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Remember? We...</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>¿Recuerdas? Nos...</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>Duración corta (959ms ≤ 1000ms) pero 18 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>00:00:19,352 --&gt; 00:00:20,311</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>I'll have no job.</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>Me quedaré sin trabajo.</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 23 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>00:00:24,733 --&gt; 00:00:25,442</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>If it weren't for him,</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>Si no fuera por él,</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>Duración corta (626ms ≤ 1000ms) pero 19 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>00:00:28,528 --&gt; 00:00:29,154</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>Come on, coach.</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>Vamos, entrenador.</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>Duración corta (542ms ≤ 1000ms) pero 18 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>00:00:35,577 --&gt; 00:00:36,119</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>No, no problem.</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>No hay problema.</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 16 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>00:01:24,959 --&gt; 00:01:25,668</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Yeah. Come here.</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>Sí. Ven aquí.</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 13 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>00:01:25,668 --&gt; 00:01:26,377</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Really sorry about it.</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>Lo siento mucho por eso.</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>Duración corta (792ms ≤ 1000ms) pero 24 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>00:01:31,883 --&gt; 00:01:32,675</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>Really sorry.</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>Lo siento mucho.</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Duración corta (500ms ≤ 1000ms) pero 16 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>00:01:32,884 --&gt; 00:01:33,384</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>You got a great arm, by the way.</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>Tienes un gran brazo, por cierto.</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>Duración corta (917ms ≤ 1000ms) pero 33 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>00:01:33,384 --&gt; 00:01:34,302</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>Son of a bitch!</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>¡Hijo de...!</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 12 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>00:01:38,389 --&gt; 00:01:39,307</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>out of the NFL.</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>a dejar la NFL.</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Duración corta (751ms ≤ 1000ms) pero 15 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>00:01:41,351 --&gt; 00:01:42,102</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>He did.</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Sí, lo hizo.</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Duración corta (501ms ≤ 1000ms) pero 12 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>00:01:45,313 --&gt; 00:01:45,814</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>I'm gonna tell on him.</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>Voy a delatarlo.</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>Duración corta (750ms ≤ 1000ms) pero 16 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>EP47</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>00:01:45,939 --&gt; 00:01:46,689</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>Damn it!</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>¡Maldita sea!</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 13 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>00:00:00,291 --&gt; 00:00:01,001</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>It was all West.</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Fue todo culpa de West.</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>Duración corta (835ms ≤ 1000ms) pero 23 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>00:00:09,300 --&gt; 00:00:10,135</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>Don't you worry that</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>¿No te preocupa que</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 19 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>00:00:22,105 --&gt; 00:00:23,023</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>is going to get you expelled</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>te vaya a expulsar</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>Duración corta (834ms ≤ 1000ms) pero 18 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>00:00:25,650 --&gt; 00:00:26,484</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>by the league?</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>de la liga?</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>Duración corta (751ms ≤ 1000ms) pero 11 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>00:00:26,484 --&gt; 00:00:27,235</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>Come join me.</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>Únete a mí.</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>Duración corta (834ms ≤ 1000ms) pero 11 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>00:00:41,958 --&gt; 00:00:42,792</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>But you know, I think you need to</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>Pero creo que debes empezar a explicar</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 38 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>00:00:54,554 --&gt; 00:00:55,472</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>immediately.</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>de inmediato.</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 13 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>00:01:05,815 --&gt; 00:01:06,524</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>Come on, man.</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>¡Vamos, hombre!</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>Duración corta (875ms ≤ 1000ms) pero 15 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>00:01:13,073 --&gt; 00:01:13,948</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>Ted, word with me.</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>Ted, háblame.</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>Duración corta (793ms ≤ 1000ms) pero 13 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>00:01:18,119 --&gt; 00:01:18,912</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>Just a joke.</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>Solo una broma.</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 15 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>00:01:23,416 --&gt; 00:01:24,334</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>I don't know. Maybe you need to</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>No sé. Tal vez necesites</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>Duración corta (876ms ≤ 1000ms) pero 24 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>00:01:26,169 --&gt; 00:01:27,045</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>I'm tired of this.</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>Estoy harto de esto.</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>Duración corta (793ms ≤ 1000ms) pero 20 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>00:01:38,014 --&gt; 00:01:38,807</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>Hey, hey, guys.</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>¡Ey, ey, chicos!</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>Duración corta (791ms ≤ 1000ms) pero 16 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>00:01:38,807 --&gt; 00:01:39,599</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>I'm sorry. Ted.</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>Lo siento, Ted.</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>Duración corta (667ms ≤ 1000ms) pero 15 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>00:01:44,979 --&gt; 00:01:45,647</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>I've got the girl.</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>Ya tengo a la chica.</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>Duración corta (917ms ≤ 1000ms) pero 20 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>EP48</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>00:01:58,785 --&gt; 00:01:59,702</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>and he nailed it.</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>y lo clavó.</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 11 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>EP5</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>00:00:02,002 --&gt; 00:00:02,919</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>Who the hell is this guy?</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>¿Quién diablos es este tipo?</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>Duración corta (792ms ≤ 1000ms) pero 28 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>EP5</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>00:00:04,254 --&gt; 00:00:05,046</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>Might as well try it.</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>Da igual, vámonos.</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 18 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>EP5</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>00:00:18,351 --&gt; 00:00:19,269</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>No way we're  coming back.</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>No hay forma de remontar.</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>Duración corta (959ms ≤ 1000ms) pero 25 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>EP5</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>00:00:19,561 --&gt; 00:00:20,520</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>Man, I hope I'm  not going to be</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>Ojalá no me dejen en el banquillo</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>Duración corta (876ms ≤ 1000ms) pero 33 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>EP5</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>00:00:43,501 --&gt; 00:00:44,377</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>to the Final Four,</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>hasta las Semifinales,</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>Duración corta (834ms ≤ 1000ms) pero 22 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>EP6</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>00:00:04,713 --&gt; 00:00:05,547</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>You can't even win against</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>Ni siquiera puedes ganar contra</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 31 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>EP6</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>00:00:20,186 --&gt; 00:00:21,104</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>Don't worry.</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>No te preocupes</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>Duración corta (584ms ≤ 1000ms) pero 15 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>EP6</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>00:00:41,249 --&gt; 00:00:41,833</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>Next game, the semifinals against the Knights.</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>El próximo partido, las semifinales contra los Caballeros</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Demasiado largo (57 chars &gt; 56 máx). Considerar simplificar o dividir con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>EP6</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>00:00:45,253 --&gt; 00:00:47,297</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>You lose that,</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>Si pierdes ese,</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>Duración corta (834ms ≤ 1000ms) pero 15 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>EP6</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>00:00:48,715 --&gt; 00:00:49,549</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>Wait a second,</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>Espera un momento,</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>Duración corta (584ms ≤ 1000ms) pero 18 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>EP6</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>00:00:56,598 --&gt; 00:00:57,182</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>How the hell did he get to</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>¿Cómo diablos llegó a</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>Duración corta (750ms ≤ 1000ms) pero 21 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>EP7</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>00:00:00,125 --&gt; 00:00:00,875</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>That Knights used to be</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>Esos Caballeros solían ser</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>Duración corta (792ms ≤ 1000ms) pero 26 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>EP7</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>00:00:03,712 --&gt; 00:00:04,504</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>fucking coach.</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>entrenador.</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>Duración corta (959ms ≤ 1000ms) pero 11 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>EP7</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>00:00:23,231 --&gt; 00:00:24,190</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>Don't you want one?</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>¿No lo quieres?</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>Duración corta (876ms ≤ 1000ms) pero 15 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>EP7</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>00:00:47,922 --&gt; 00:00:48,798</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>You all want Ted back?</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>¿Todos quieren a Ted de vuelta?</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 31 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>EP7</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>00:00:50,550 --&gt; 00:00:51,259</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>I guess I can't risk him</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>supongo que no puedo arriesgarme a que</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>Duración corta (751ms ≤ 1000ms) pero 38 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>EP7</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>00:01:00,518 --&gt; 00:01:01,269</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>leaking my playbook.</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>filtre mi estrategia.</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>Duración corta (876ms ≤ 1000ms) pero 21 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>EP7</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>00:01:01,269 --&gt; 00:01:02,145</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>Mr. Vincent,</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>Señor Vincent,</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>Duración corta (834ms ≤ 1000ms) pero 14 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>EP7</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>00:01:11,738 --&gt; 00:01:12,572</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>What are you doing here?</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>¿Qué haces aquí?</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 16 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>00:00:00,333 --&gt; 00:00:01,251</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>I'll let you crawl back and</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>te deje arrastrarte de vuelta y</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>Duración corta (960ms ≤ 1000ms) pero 31 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>00:00:11,761 --&gt; 00:00:12,721</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>You want our head coach to</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>¿Quieres que nuestro entrenador jefe se</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Duración corta (917ms ≤ 1000ms) pero 39 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>00:00:16,725 --&gt; 00:00:17,642</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>apologize to you?</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>disculpe contigo?</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 17 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>00:00:17,642 --&gt; 00:00:18,560</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>Guys like you,</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>Tipos como tú,</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>Duración corta (959ms ≤ 1000ms) pero 14 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>00:00:36,953 --&gt; 00:00:37,912</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>born at the bottom,</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>nacidos en lo bajo,</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>Duración corta (792ms ≤ 1000ms) pero 19 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>00:00:37,996 --&gt; 00:00:38,788</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>don't get to be champions ever.</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>nunca llegan a ser campeones.</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Duración corta (667ms ≤ 1000ms) pero 29 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>00:00:40,165 --&gt; 00:00:40,832</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>She's right.</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>Tiene razón.</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 12 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>00:00:41,249 --&gt; 00:00:41,958</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>Like the Knights.</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>Como los Caballeros.</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 20 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>00:00:47,255 --&gt; 00:00:47,964</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>What is this?</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>¿Qué es esto?</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Duración corta (625ms ≤ 1000ms) pero 13 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>00:00:54,596 --&gt; 00:00:55,221</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>whole damn team.</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>Todo el equipo maldito.</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 23 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>00:01:05,982 --&gt; 00:01:06,691</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>You'll never beat us.</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>Nunca nos vencerás.</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Duración corta (750ms ≤ 1000ms) pero 19 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>00:01:08,193 --&gt; 00:01:08,943</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>you're doing this for the raise.</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>lo haces por el aumento.</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Duración corta (959ms ≤ 1000ms) pero 24 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>00:01:22,791 --&gt; 00:01:23,750</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>Is that all you've got?</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>Eso es todo lo que tienes</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Duración corta (960ms ≤ 1000ms) pero 25 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>00:01:39,641 --&gt; 00:01:40,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>the Knights to victory.</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>a los Caballeros a la victoria</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 30 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>EP8</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>00:01:52,570 --&gt; 00:01:53,488</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>No way...</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>¡No puede ser...</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>Duración corta (751ms ≤ 1000ms) pero 16 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>00:00:05,630 --&gt; 00:00:06,381</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>This has to be fake.</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>Esto tiene que ser una broma.</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Duración corta (959ms ≤ 1000ms) pero 29 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>00:00:12,429 --&gt; 00:00:13,388</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>So the Eagles want to bring back a fired coach?</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>¿Así que los Águilas quieren traer de vuelta a un entrenador despedido?</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Demasiado largo (71 chars &gt; 56 máx). Considerar simplificar o dividir con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>00:00:19,269 --&gt; 00:00:21,646</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>Just wait, Ted.</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>Espera, Ted.</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>Duración corta (876ms ≤ 1000ms) pero 12 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>00:00:51,301 --&gt; 00:00:52,177</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>Coach,</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>Entrenador,</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Duración corta (669ms ≤ 1000ms) pero 11 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>00:01:51,861 --&gt; 00:01:52,529</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>Hands in the middle.</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>Manos en el centro.</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>Duración corta (750ms ≤ 1000ms) pero 19 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>00:01:57,826 --&gt; 00:01:58,576</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>It's for poor people.</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>Es para gente pobre.</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 20 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>00:02:17,053 --&gt; 00:02:17,762</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>People of class.</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>Gente con clase.</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Duración corta (876ms ≤ 1000ms) pero 16 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>00:02:18,054 --&gt; 00:02:18,930</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>I need a win.</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>Necesito ganar.</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Duración corta (751ms ≤ 1000ms) pero 15 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>00:02:29,732 --&gt; 00:02:30,483</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Forty million.</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Cuarenta millones.</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Duración corta (709ms ≤ 1000ms) pero 18 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>00:02:40,577 --&gt; 00:02:41,286</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>To victory.</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>A la victoria.</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>Duración corta (876ms ≤ 1000ms) pero 14 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>00:02:54,007 --&gt; 00:02:54,883</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Right from the start,</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>Desde el principio,</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Duración corta (918ms ≤ 1000ms) pero 19 chars (recomendado ≤10). Considerar fusionar con subtítulo adyacente.</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>EP9</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>00:03:16,779 --&gt; 00:03:17,697</t>
         </is>
       </c>
     </row>
